--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -547,8 +547,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>16385.6</v>
+        <v>16374.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.35</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>701.7387580299785</v>
+        <v>701.5809768637532</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1388318534865847</v>
+        <v>0.13847673977909</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04282655246252676</v>
+        <v>0.04284490145672665</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>75.53274139463386</v>
+        <v>75.39069591163602</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>80.46285272142045</v>
+        <v>80.4202390765211</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>24.45247582045317</v>
+        <v>24.45010163166592</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17159.25001300289</v>
+        <v>17153.72618716222</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.0472152385633049</v>
+        <v>0.04756219501567771</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>27.62171317564521</v>
+        <v>27.61459060928346</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19383.22669853756</v>
+        <v>19373.87145535372</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1829427484216364</v>
+        <v>0.183144413422599</v>
       </c>
     </row>
     <row r="15"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3923,6 +3923,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>16374.9</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.174242424242</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.138476739779</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>16374.9</v>
+        <v>16334.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.34</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.1742424242424243</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>701.5809768637532</v>
+        <v>701.6473367697595</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.13847673977909</v>
+        <v>0.1386849609214822</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04284490145672665</v>
+        <v>0.0429553264604811</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>82.57575757575756</v>
+        <v>84.09090909090909</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>75.39069591163602</v>
+        <v>75.47398436859288</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>80.4202390765211</v>
+        <v>81.50583167421422</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>24.45010163166592</v>
+        <v>24.4514937387322</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17153.72618716222</v>
+        <v>17156.32546182389</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.04756219501567771</v>
+        <v>0.05032189599365089</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>27.61459060928346</v>
+        <v>27.6187669304823</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19373.87145535372</v>
+        <v>19378.63426163761</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.183144413422599</v>
+        <v>0.1863731499348069</v>
       </c>
     </row>
     <row r="15"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3956,6 +3956,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>16334.35</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.159090909091</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.138684960921</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>16334.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>23.28</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.1590909090909091</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>701.6473367697595</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.1386849609214822</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>84.09090909090909</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>75.47398436859288</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>81.50583167421422</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>24.4514937387322</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>17156.32546182389</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.05032189599365089</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>27.6187669304823</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>19378.63426163761</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.1863731499348069</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.2662432014886371</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1994931426521214</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.2620176187134372</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.2562624052644633</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1708810140258157</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2105273557405587</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,17 +857,17 @@
       <c r="B20" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.003521828810183036</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1941157391430326</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1711753432147336</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,17 +880,17 @@
       <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.03356378290529483</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1330013384186792</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1100952663254819</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,21 +903,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.133962114272929</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.2211051188007948</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1842961236465905</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1038,16 +1052,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>7992.27</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>36.87</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1057,16 +1071,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>8521.200000000001</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>32.9</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1076,16 +1090,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>8768.450000000001</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.45</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1095,16 +1109,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>8930.27</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>30.66</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1114,16 +1128,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>9391.65</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>27.46</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1133,16 +1147,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>9797.049999999999</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>29.75</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1152,16 +1166,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>9819.549999999999</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>28.48</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1171,16 +1185,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>9580.5</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>26.19</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1190,16 +1204,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>9814.15</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>26.94</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1209,16 +1223,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>9738.950000000001</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>26.37</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1228,16 +1242,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>9253.5</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>23.89</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1247,16 +1261,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>9650.200000000001</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>24.82</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1266,16 +1280,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>9625.549999999999</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>24.45</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1285,16 +1299,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>9183.549999999999</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>22.01</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1304,16 +1318,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>8705.950000000001</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>21.02</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1323,16 +1337,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>9607.299999999999</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>22.66</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1342,16 +1356,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>10092.6</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>23.74</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1361,16 +1375,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>9815.5</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>22.9</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1380,16 +1394,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>10131.25</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>23.19</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1399,16 +1413,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>10415.9</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>24.72</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1418,16 +1432,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>10143.55</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>24.28</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1437,16 +1451,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>9837.799999999999</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>23.24</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1456,16 +1470,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>9615.6</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>22.42</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1475,16 +1489,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>9618.9</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>22.28</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1494,16 +1508,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>10070.35</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>23.12</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1513,16 +1527,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>10508.1</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>23.69</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1532,16 +1546,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>11023.85</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>24.77</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1551,16 +1565,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>11495.15</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>25.55</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1570,16 +1584,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>11587.05</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>23.92</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1589,16 +1603,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>11877.5</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>24.58</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1608,16 +1622,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>11487.45</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>22.85</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1627,16 +1641,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>12389.8</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>23.32</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1646,16 +1660,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>13347</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>25.06</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1665,16 +1679,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>13703.45</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>25.13</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1684,16 +1698,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>13826.85</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>25.05</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1703,16 +1717,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>13921.1</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>27.46</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1722,16 +1736,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>14520.25</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>27.83</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1741,16 +1755,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>14708.6</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>28.67</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1760,16 +1774,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>15756.45</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>30.28</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1779,16 +1793,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>16466.25</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>31.61</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1798,16 +1812,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>16568.95</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>31.46</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1817,16 +1831,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>16910.05</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>32.24</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1836,16 +1850,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>15790.55</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>30.16</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1855,16 +1869,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>15800.2</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>29.59</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1874,16 +1888,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>15714.8</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>29.48</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1893,16 +1907,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>15092.3</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>27.64</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1912,16 +1926,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>13805.6</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>24.61</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1931,16 +1945,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>14821.1</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>26.18</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1950,16 +1964,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>15355.15</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>26.69</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1969,16 +1983,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>15994.95</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>27.11</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1988,16 +2002,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>16572.25</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>27.72</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2007,16 +2021,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>16095.25</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>26.55</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2026,16 +2040,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>15745.15</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>25.55</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2045,16 +2059,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>15946.5</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>26.02</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2064,16 +2078,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>16666.75</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>26.96</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2083,16 +2097,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>16915.1</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>26.79</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2102,16 +2116,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>16854.95</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>26.79</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2121,16 +2135,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>16309</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>25.69</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2140,16 +2154,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>16442.55</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>25.98</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2159,16 +2173,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>14574.5</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>23.55</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2178,16 +2192,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>16181.9</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>25.69</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2197,16 +2211,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>16304.65</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>23.86</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2216,16 +2230,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>16476.35</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>23.88</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2235,16 +2249,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>16796.85</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>24.51</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2254,16 +2268,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>16858.65</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>24.03</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2365,13 +2379,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>6145.35</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>37.55</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2379,12 +2393,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2392,28 +2406,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>5705.9</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>34.51</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2421,12 +2435,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2434,28 +2448,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>5768.36</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>33.94</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2463,12 +2477,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2476,28 +2490,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>5667.51</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>33.54</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2505,12 +2519,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2518,28 +2532,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>5763.86</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>32.64</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2547,15 +2561,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2563,28 +2577,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>6011.71</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>32.52</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2592,15 +2606,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2608,28 +2622,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>5960.89</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>31.59</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2637,15 +2651,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2653,28 +2667,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>5687.47</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>27.11</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2682,15 +2696,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2698,28 +2712,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>6045.55</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>28.73</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2727,15 +2741,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2743,28 +2757,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>4304.47</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>20.51</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2772,15 +2786,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2788,28 +2802,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>5276.28</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>38.42</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2817,15 +2831,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2833,28 +2847,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>5902.99</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>78.3</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2862,15 +2876,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2878,28 +2892,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>7234.79</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>60.9</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2907,15 +2921,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2923,28 +2937,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>7935.05</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>37.22</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2952,15 +2966,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2968,28 +2982,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>8768.450000000001</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>31.45</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2997,15 +3011,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3013,28 +3027,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>9797.049999999999</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>29.75</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3042,15 +3056,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3058,25 +3072,25 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
+      <c r="K17" s="30" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>9814.15</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>26.94</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3084,15 +3098,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3100,25 +3114,25 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>9650.200000000001</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>24.82</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3126,15 +3140,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3142,25 +3156,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>8705.950000000001</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>21.02</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3168,15 +3182,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3184,25 +3198,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>9815.5</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3210,15 +3224,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3226,25 +3240,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>10143.55</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>24.28</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3252,15 +3266,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3268,25 +3282,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>9618.9</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>22.28</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3294,15 +3308,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3310,25 +3324,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>11023.85</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>24.77</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3336,15 +3350,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3352,25 +3366,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>11877.5</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>24.58</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3378,15 +3392,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3394,22 +3408,22 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="J25" s="30" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>13347</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>25.06</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3417,15 +3431,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3433,22 +3447,22 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>13921.1</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>27.46</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3456,15 +3470,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3472,22 +3486,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>15756.45</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>30.28</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3495,15 +3509,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3511,22 +3525,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>16910.05</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>32.24</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3534,15 +3548,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3550,22 +3564,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>15714.8</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>29.48</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3573,15 +3587,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3589,22 +3603,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>14821.1</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>26.18</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3612,15 +3626,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3628,22 +3642,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>16572.25</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>27.72</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3651,15 +3665,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3667,22 +3681,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>15946.5</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>26.02</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3690,15 +3704,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3706,19 +3720,19 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>16854.95</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.79</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3726,15 +3740,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3742,19 +3756,19 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>14574.5</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>23.55</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3762,15 +3776,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3778,19 +3792,19 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>16476.35</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>23.88</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3798,15 +3812,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3814,10 +3828,10 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3894,30 +3908,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>16385.6</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>23.35</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.174242424242</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.138831853487</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -3927,30 +3941,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>16374.9</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>23.34</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.174242424242</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.138476739779</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -3960,30 +3974,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>16334.35</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>23.28</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.159090909091</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.138684960921</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4103,4 +4117,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Largemidcap 250 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4016,6 +4019,5112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E255"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY LargeMidcap 250 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3M India Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ABB India Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Abbott India Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ACC Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adani Energy Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adani Green Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Adani Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Adani Total Gas Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AIA Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AIAENG</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ajanta Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ambuja Cements Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anthem Biosciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Apar Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>APL Apollo Tubes Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Apollo Tyres Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asian Paints Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Astral Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AU Small Finance Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AIIL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AWL Agri Business Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AWL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Axis Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bajaj Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bajaj Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BAJAJHFL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Balkrishna Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bank of Baroda</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bank of India</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bank of Maharashtra</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Berger Paints India Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bharat Forge Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bharti Hexacom Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BHARTIHEXA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Billionbrains Garage Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Biocon Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Blue Star Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bosch Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Britannia Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BSE Ltd.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Canara Bank</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cipla Ltd.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Coal India Ltd.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Ltd.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Coforge Ltd.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Container Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Coromandel International Ltd.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CRISIL Ltd.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cummins India Ltd.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Dabur India Ltd.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Dalmia Bharat Ltd.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Dixon Technologies (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>DLF Ltd.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Endurance Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ENDURANCE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Ltd.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Eternal Ltd.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Exide Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Federal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare Ltd.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FSN E-Commerce Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GAIL (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GE Vernova T&amp;D India Ltd.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>General Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GICRE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GLAXO</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Global Health Ltd.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MEDANTA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GMR Airports Ltd.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Godfrey Phillips India Ltd.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Godrej Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GODREJIND</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Godrej Properties Ltd.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Grasim Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Gujarat Fluorochemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FLUOROCHEM</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Havells India Ltd.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HDB Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HDBFS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HDFC Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HDFC Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hexaware Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HEXT</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hindalco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hindustan Aeronautics Ltd.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Ltd.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hitachi Energy India Ltd.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Honeywell Automation India Ltd.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>HONAUT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Hyundai Motor India Ltd.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ICICI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ICICIAMC</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IDFC First Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Indian Bank</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Indian Hotels Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Indian Oil Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Indian Railway Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Indian Renewable Energy Development Agency Ltd.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>IREDA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Indus Towers Ltd.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IndusInd Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Info Edge (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Infosys Ltd.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>124</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>InterGlobe Aviation Ltd.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>125</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>126</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ITC Hotels Ltd.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ITCHOTELS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>J.K. Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>JKCEMENT</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Jindal Stainless Ltd.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>130</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Jindal Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>131</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Jio Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>132</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JSW Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>133</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>JSW Infrastructure Ltd.</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>JSWINFRA</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>134</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>JSW Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>135</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Jubilant Foodworks Ltd.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>136</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>K.P.R. Mill Ltd.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>137</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers India Ltd.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>138</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>KEI Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>139</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>KPIT Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>141</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>L&amp;T Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Ltd.</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Laurus Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lenskart Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>LG Electronics India Ltd.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>LIC Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Linde India Ltd.</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LINDEINDIA</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Lloyds Metals And Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>151</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Lodha Developers Ltd.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>152</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>LTM Ltd.</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>153</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>155</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>156</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Mankind Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>157</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>158</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>159</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Max Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>160</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Max Healthcare Institute Ltd.</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>161</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>162</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>163</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>MphasiS Ltd.</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>164</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>MRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>165</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>166</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Muthoot Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>167</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>National Aluminium Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>168</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>169</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>NHPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>170</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Nippon Life India Asset Management Ltd.</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>NLC India Ltd.</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>172</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>NMDC Ltd.</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>173</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>NTPC Green Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NTPCGREEN</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>174</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>NTPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>175</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Ltd.</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>176</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>177</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Oil India Ltd.</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>178</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>One 97 Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>179</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ONE WAM Ltd.</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>180</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Oracle Financial Services Software Ltd.</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>181</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Page Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>182</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Patanjali Foods Ltd.</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>183</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PB Fintech Ltd.</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>184</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Persistent Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>185</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Petronet LNG Ltd.</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>186</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Phoenix Mills Ltd.</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>187</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PI Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>188</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Pidilite Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>189</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd.</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>190</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>191</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>192</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Premier Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>193</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Prestige Estates Projects Ltd.</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>194</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Punjab National Bank</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>195</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Radico Khaitan Ltd</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>196</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Rail Vikas Nigam Ltd.</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>197</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>REC Ltd.</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>198</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>199</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson International Ltd.</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>200</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SBI Cards and Payment Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>201</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SBI Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>202</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Schaeffler India Ltd.</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>203</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Shree Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>204</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Shriram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>205</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Siemens Energy India Ltd.</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ENRIN</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>206</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Siemens Ltd.</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>207</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SJVN Ltd.</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>208</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Solar Industries India Ltd.</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>209</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>210</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>211</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Steel Authority of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>212</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>213</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sundaram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>214</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Supreme Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>215</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Suzlon Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>216</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Swiggy Ltd.</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SWIGGY</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>217</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Tata Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>218</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Tata Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>219</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>220</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Tata Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>221</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Tata Elxsi Ltd.</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>222</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Tata Investment Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>223</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Tata Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>224</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>225</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Tata Power Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>226</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Tata Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>227</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>228</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>The New India Assurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>229</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Thermax Ltd.</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>230</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Titan Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>231</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>232</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Torrent Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>233</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Trent Ltd.</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>234</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Tube Investments of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>235</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>236</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>UltraTech Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>237</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Union Bank of India</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>238</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>United Breweries Ltd.</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>239</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>United Spirits Ltd.</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>240</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>UNO Minda Ltd.</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>241</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>UPL Ltd.</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>242</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Varun Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>243</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Vedanta Ltd.</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>244</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Vishal Mega Mart Ltd.</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>245</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Ltd.</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>246</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Voltas Ltd.</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>247</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Waaree Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>248</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Wipro Ltd.</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>249</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Yes Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>250</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4117,43 +9226,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Largemidcap 250 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16334.35</v>
+        <v>16432.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.28</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1590909090909091</v>
+        <v>0.1742424242424243</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>701.6473367697595</v>
+        <v>701.6545687446626</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1386849609214822</v>
+        <v>0.1384407673155428</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0429553264604811</v>
+        <v>0.04269854824935952</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>84.09090909090909</v>
+        <v>82.57575757575756</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.47398436859288</v>
+        <v>75.37630692621711</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.50583167421422</v>
+        <v>80.41592238089542</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.4514937387322</v>
+        <v>24.44960653514871</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17156.32546182389</v>
+        <v>17155.17812939645</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05032189599365089</v>
+        <v>0.04396270431890303</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.6187669304823</v>
+        <v>27.61386910444318</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19378.63426163761</v>
+        <v>19375.39741784964</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1863731499348069</v>
+        <v>0.1790721223075651</v>
       </c>
     </row>
     <row r="16">
@@ -3849,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4006,6 +4006,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>16432.75</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.174242424242</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.138440767316</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16432.75</v>
+        <v>16135.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1742424242424243</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>701.6545687446626</v>
+        <v>701.545652173913</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1384407673155428</v>
+        <v>0.1384107946026987</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04269854824935952</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>82.57575757575756</v>
+        <v>88.63636363636364</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.37630692621711</v>
+        <v>75.36431784107947</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.41592238089542</v>
+        <v>84.65474989777839</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.44960653514871</v>
+        <v>24.44903876633112</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17155.17812939645</v>
+        <v>17152.11684635105</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04396270431890303</v>
+        <v>0.06300168549265739</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.61386910444318</v>
+        <v>27.61326793745985</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19375.39741784964</v>
+        <v>19371.96806383827</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1790721223075651</v>
+        <v>0.2005768668460803</v>
       </c>
     </row>
     <row r="16">
@@ -3849,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4039,6 +4039,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>16135.55</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.113636363636</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.138410794603</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4079,7 +4112,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16135.55</v>
+        <v>16153.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>701.545652173913</v>
+        <v>701.7180712423979</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1384107946026987</v>
+        <v>0.1385338037026338</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04344048653344917</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.36431784107947</v>
+        <v>75.41352148105352</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>84.65474989777839</v>
+        <v>84.6695109897706</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.44903876633112</v>
+        <v>24.45048314475475</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17152.11684635105</v>
+        <v>17157.34587328206</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06300168549265739</v>
+        <v>0.06214088378604465</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.61326793745985</v>
+        <v>27.61573514854997</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19371.96806383827</v>
+        <v>19378.46040438138</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2005768668460803</v>
+        <v>0.199640970831884</v>
       </c>
     </row>
     <row r="16">
@@ -3849,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4072,6 +4072,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>16153.55</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.113636363636</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.138533803703</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4112,7 +4145,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16153.55</v>
+        <v>15888.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.02</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>701.7180712423979</v>
+        <v>701.797703180212</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1385338037026338</v>
+        <v>0.138861836016176</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04344048653344917</v>
+        <v>0.0441696113074205</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.63636363636364</v>
+        <v>93.18181818181819</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.41352148105352</v>
+        <v>75.54473440647038</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>84.6695109897706</v>
+        <v>87.89069304921385</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.45048314475475</v>
+        <v>24.45267627507958</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17157.34587328206</v>
+        <v>17160.83204646011</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06214088378604465</v>
+        <v>0.08006520649644777</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.61573514854997</v>
+        <v>27.62231453952445</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19378.46040438138</v>
+        <v>19385.27690035963</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.199640970831884</v>
+        <v>0.2200668966221044</v>
       </c>
     </row>
     <row r="16">
@@ -3849,13 +3849,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -4105,6 +4105,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>15888.7</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.0681818181818</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.138861836016</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4145,7 +4178,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15888.7</v>
+        <v>15773.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.64</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>701.797703180212</v>
+        <v>701.6703736654804</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.138861836016176</v>
+        <v>0.1388202594728114</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0441696113074205</v>
+        <v>0.04448398576512456</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.54473440647038</v>
+        <v>75.52810378912456</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>87.89069304921385</v>
+        <v>87.8857038640101</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.45267627507958</v>
+        <v>24.45239830618965</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17160.83204646011</v>
+        <v>17157.52345652125</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08006520649644777</v>
+        <v>0.08774013817569615</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.62231453952445</v>
+        <v>27.62148063285467</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19385.27690035963</v>
+        <v>19381.17463684897</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2200668966221044</v>
+        <v>0.228713551283571</v>
       </c>
     </row>
     <row r="16">
@@ -3849,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4138,6 +4138,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>15773.55</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.0681818181818</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.138820259473</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4178,7 +4211,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4248,17 +4281,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3M India Ltd.</t>
+          <t>ABB India Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4268,17 +4301,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ABB India Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4288,17 +4321,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Adani Energy Solutions Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4341,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACC Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4361,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adani Energy Solutions Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4348,17 +4381,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4401,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Adani Power Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4388,17 +4421,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Ltd.</t>
+          <t>Adani Total Gas Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4408,17 +4441,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adani Power Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4461,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adani Total Gas Ltd.</t>
+          <t>AIA Engineering Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4448,17 +4481,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Ajanta Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4468,17 +4501,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AIA Engineering Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4488,17 +4521,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ajanta Pharmaceuticals Ltd.</t>
+          <t>Ambuja Cements Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4541,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4528,17 +4561,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ambuja Cements Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4548,17 +4581,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4568,17 +4601,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4621,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4608,17 +4641,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4628,17 +4661,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>Aster DM Quality Care Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4681,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>Astral Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4668,17 +4701,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4721,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Astral Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4741,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4728,17 +4761,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4781,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AIIL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4768,17 +4801,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4788,17 +4821,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4808,12 +4841,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4828,17 +4861,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4848,12 +4881,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4868,17 +4901,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Balkrishna Industries Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4888,12 +4921,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4908,12 +4941,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Bank of India</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4928,17 +4961,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4981,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Berger Paints India Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4968,17 +5001,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bank of India</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4988,17 +5021,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5008,17 +5041,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5028,12 +5061,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5048,17 +5081,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Bharat Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5068,17 +5101,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5121,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Bharti Hexacom Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARTIHEXA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5108,17 +5141,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd.</t>
+          <t>Billionbrains Garage Ventures Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>GROWW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5128,17 +5161,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Biocon Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5181,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bharti Hexacom Ltd.</t>
+          <t>Blue Star Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5168,17 +5201,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Billionbrains Garage Ventures Ltd.</t>
+          <t>Bosch Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GROWW</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5221,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Biocon Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5208,17 +5241,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blue Star Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5228,17 +5261,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bosch Ltd.</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5281,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5301,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5288,17 +5321,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5308,17 +5341,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Coal India Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5328,17 +5361,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+          <t>Cochin Shipyard Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5348,17 +5381,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5368,17 +5401,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Coal India Ltd.</t>
+          <t>Colgate Palmolive (India) Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5388,17 +5421,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5408,17 +5441,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5428,17 +5461,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5448,17 +5481,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Container Corporation of India Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5468,17 +5501,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Dabur India Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5488,17 +5521,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CRISIL Ltd.</t>
+          <t>Dalmia Bharat Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5541,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>Divi's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5528,17 +5561,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5548,17 +5581,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5568,12 +5601,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5588,17 +5621,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5641,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>EMBASSY OFFICE PARKS REIT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>EMBASSY</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5628,17 +5661,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Endurance Technologies Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5648,17 +5681,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5668,17 +5701,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5688,17 +5721,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>Exide Industries Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5741,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5728,17 +5761,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>Fertilisers and Chemicals Travancore Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5748,17 +5781,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5768,17 +5801,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5788,17 +5821,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5808,17 +5841,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>GE Vernova T&amp;D India Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5828,17 +5861,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Ltd.</t>
+          <t>General Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5848,17 +5881,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5901,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5888,12 +5921,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5908,17 +5941,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5928,17 +5961,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GMR Airports Ltd.</t>
+          <t>Godfrey Phillips India Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5981,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Godfrey Phillips India Ltd.</t>
+          <t>Godrej Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5968,17 +6001,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Ltd.</t>
+          <t>Godrej Industries Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>GODREJIND</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Diversified</t>
         </is>
       </c>
     </row>
@@ -5988,17 +6021,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Godrej Industries Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GODREJIND</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6041,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -6028,17 +6061,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Gujarat Fluorochemicals Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6081,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6068,17 +6101,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6088,17 +6121,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6108,12 +6141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6128,12 +6161,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6148,12 +6181,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6168,17 +6201,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6188,17 +6221,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Hexaware Technologies Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6241,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hexaware Technologies Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6228,17 +6261,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>Hindustan Aeronautics Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6248,17 +6281,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6348,17 +6381,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Ltd.</t>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6368,17 +6401,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+          <t>Hyundai Motor India Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6388,17 +6421,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hyundai Motor India Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6441,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6428,12 +6461,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6448,12 +6481,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6468,12 +6501,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6488,12 +6521,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6508,17 +6541,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6528,17 +6561,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Indian Oil Corporation Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6548,17 +6581,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation Ltd.</t>
+          <t>Indian Overseas Bank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7028,17 +7061,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>KPIT Technologies Ltd.</t>
+          <t>L&amp;T Finance Ltd.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7048,17 +7081,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Ltd.</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7068,17 +7101,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7121,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7108,17 +7141,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>Lenskart Solutions Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7128,17 +7161,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lenskart Solutions Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7148,17 +7181,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7168,12 +7201,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7188,17 +7221,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Linde India Ltd.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -7208,17 +7241,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -7228,17 +7261,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -7248,17 +7281,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lodha Developers Ltd.</t>
+          <t>LTM Ltd.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7268,17 +7301,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LTM Ltd.</t>
+          <t>Lupin Ltd.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7288,17 +7321,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lupin Ltd.</t>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7308,17 +7341,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7328,17 +7361,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Mankind Pharma Ltd.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7348,17 +7381,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>Marico Ltd.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7368,17 +7401,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Marico Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7388,17 +7421,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Max Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7408,17 +7441,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7428,17 +7461,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7448,17 +7481,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Meesho Ltd.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7568,17 +7601,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7588,17 +7621,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -7608,17 +7641,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7628,17 +7661,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nippon Life India Asset Management Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -7648,17 +7681,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Nippon Life India Asset Management Ltd.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7668,17 +7701,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7721,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -7708,12 +7741,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7728,17 +7761,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -7748,17 +7781,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7801,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oil India Ltd.</t>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7788,17 +7821,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>Oil India Ltd.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7841,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ONE WAM Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7828,17 +7861,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7848,17 +7881,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7868,17 +7901,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Patanjali Foods Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -7888,17 +7921,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PB Fintech Ltd.</t>
+          <t>Patanjali Foods Ltd.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7908,17 +7941,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Persistent Systems Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7928,17 +7961,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>Persistent Systems Ltd.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7948,17 +7981,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -7968,17 +8001,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PI Industries Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -7988,12 +8021,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>PI Industries Ltd.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8008,17 +8041,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -8028,12 +8061,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8048,17 +8081,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Polycab India Ltd.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8068,17 +8101,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Premier Energies Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8088,17 +8121,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Prestige Estates Projects Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -8108,17 +8141,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Premier Energies Ltd.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8128,17 +8161,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Prestige Estates Projects Ltd.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -8148,17 +8181,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Rail Vikas Nigam Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8168,17 +8201,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8188,17 +8221,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>Rail Vikas Nigam Ltd.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8208,17 +8241,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8228,17 +8261,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8281,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Samvardhana Motherson International Ltd.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8268,17 +8301,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8288,17 +8321,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8341,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8328,17 +8361,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Siemens Energy India Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -8348,17 +8381,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Siemens Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8368,17 +8401,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SJVN Ltd.</t>
+          <t>Siemens Energy India Ltd.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>ENRIN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8388,17 +8421,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Solar Industries India Ltd.</t>
+          <t>Siemens Ltd.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8441,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>Solar Industries India Ltd.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8428,17 +8461,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>SRF Ltd.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -8448,17 +8481,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8468,17 +8501,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8488,17 +8521,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Sundaram Finance Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8508,17 +8541,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Sundaram Finance Ltd.</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8561,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Suzlon Energy Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -8548,17 +8581,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Swiggy Ltd.</t>
+          <t>Suzlon Energy Ltd.</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8568,17 +8601,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Tata Capital Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -8588,17 +8621,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>Tata Capital Ltd.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8608,17 +8641,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8661,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -8648,17 +8681,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8788,17 +8821,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>Thermax Ltd.</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8808,17 +8841,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Thermax Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -8828,17 +8861,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8848,17 +8881,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -8868,17 +8901,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -8888,17 +8921,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8908,12 +8941,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>TVS Motor Company Ltd.</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -8928,17 +8961,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TVS Motor Company Ltd.</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -8948,17 +8981,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8968,17 +9001,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>United Breweries Ltd.</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8988,12 +9021,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>United Breweries Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -9008,17 +9041,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>UNO Minda Ltd.</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9061,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>UNO Minda Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -9048,17 +9081,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9068,17 +9101,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Vedanta Aluminium Metal Ltd.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15773.55</v>
+        <v>15757.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.48</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.1044776119402985</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>701.6703736654804</v>
+        <v>689.313210848644</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1388202594728114</v>
+        <v>0.1247565137354099</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04448398576512456</v>
+        <v>0.04374453193350832</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.18181818181819</v>
+        <v>89.55223880597015</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.52810378912456</v>
+        <v>69.90260549416394</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>87.8857038640101</v>
+        <v>83.65734881242828</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.45239830618965</v>
+        <v>24.00496963951842</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17157.52345652125</v>
+        <v>16546.94269854066</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08774013817569615</v>
+        <v>0.05008616095881102</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.62148063285467</v>
+        <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19381.17463684897</v>
+        <v>18928.54076990376</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.228713551283571</v>
+        <v>0.2012248468941382</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="30" t="n">
         <v>0.2562624052644633</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1708810140258157</v>
+        <v>0.1571111742810757</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.2105273557405587</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.003521828810183036</v>
+        <v>0.0001391863580043617</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.1941157391430326</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="30" t="n">
         <v>0.03356378290529483</v>
@@ -913,7 +913,7 @@
         <v>0.2211051188007948</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.1842961236465905</v>
+        <v>0.1593760349462473</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2286,6 +2286,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>15757.7</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2402,7 +2421,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,C2)+1)/2)/COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2444,7 +2463,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,C3)+1)/2)/COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2486,7 +2505,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,C4)+1)/2)/COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2528,7 +2547,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,C5)+1)/2)/COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2573,7 +2592,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,C6)+1)/2)/COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2618,7 +2637,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,C7)+1)/2)/COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2663,7 +2682,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,C8)+1)/2)/COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2708,7 +2727,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,C9)+1)/2)/COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2753,7 +2772,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,C10)+1)/2)/COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2798,7 +2817,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,C11)+1)/2)/COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2843,7 +2862,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,C12)+1)/2)/COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2888,7 +2907,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,C13)+1)/2)/COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2933,7 +2952,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,C14)+1)/2)/COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2978,7 +2997,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,C15)+1)/2)/COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3023,7 +3042,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,C16)+1)/2)/COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3068,7 +3087,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,C17)+1)/2)/COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3083,7 +3102,10 @@
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="30" t="n"/>
+      <c r="K17" s="30">
+        <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
@@ -3110,7 +3132,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,C18)+1)/2)/COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3152,7 +3174,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,C19)+1)/2)/COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3194,7 +3216,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,C20)+1)/2)/COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3236,7 +3258,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,C21)+1)/2)/COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3278,7 +3300,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,C22)+1)/2)/COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3320,7 +3342,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,C23)+1)/2)/COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3362,7 +3384,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,C24)+1)/2)/COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3404,7 +3426,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,C25)+1)/2)/COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3415,7 +3437,10 @@
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="30" t="n"/>
+      <c r="J25" s="30">
+        <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K25" s="30" t="n"/>
       <c r="L25" s="30" t="n"/>
     </row>
@@ -3443,7 +3468,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,C26)+1)/2)/COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3482,7 +3507,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,C27)+1)/2)/COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3521,7 +3546,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,C28)+1)/2)/COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3560,7 +3585,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,C29)+1)/2)/COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3599,7 +3624,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,C30)+1)/2)/COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3638,7 +3663,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,C31)+1)/2)/COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3677,7 +3702,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,C32)+1)/2)/COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3716,14 +3741,17 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,C33)+1)/2)/COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="30" t="n"/>
+      <c r="I33" s="30">
+        <f>IFERROR(B37/B33-1,"")</f>
+        <v/>
+      </c>
       <c r="J33" s="30" t="n"/>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
@@ -3752,7 +3780,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,C34)+1)/2)/COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3788,7 +3816,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,C35)+1)/2)/COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3824,7 +3852,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,C36)+1)/2)/COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3835,6 +3863,42 @@
       <c r="J36" s="30" t="n"/>
       <c r="K36" s="30" t="n"/>
       <c r="L36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <v>15757.7</v>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E37" s="33">
+        <f>IFERROR(B37/C37,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,C37)+1)/2)/COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3849,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3857,7 +3921,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4171,6 +4235,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>15757.7</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.10447761194</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.124756513735</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4211,7 +4308,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15757.7</v>
+        <v>15604.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.86</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1044776119402985</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.313210848644</v>
+        <v>689.2535335689046</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1247565137354099</v>
+        <v>0.1246925828453131</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04374453193350832</v>
+        <v>0.0441696113074205</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>89.55223880597015</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>69.90260549416394</v>
+        <v>69.87703313812526</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.65734881242828</v>
+        <v>86.26161740412414</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.00496963951842</v>
+        <v>24.00417397392624</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16546.94269854066</v>
+        <v>16544.9617319314</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05008616095881102</v>
+        <v>0.06025503418402134</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18928.54076990376</v>
+        <v>18926.90203180212</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2012248468941382</v>
+        <v>0.2128975265017667</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4268,6 +4268,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>15604.7</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.124692582845</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4308,7 +4341,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15604.7</v>
+        <v>15687.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.64</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.2535335689046</v>
+        <v>689.2640597539543</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1246925828453131</v>
+        <v>0.1249132513231015</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0441696113074205</v>
+        <v>0.04393673110720562</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>69.87703313812526</v>
+        <v>69.96530052924059</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>86.26161740412414</v>
+        <v>85.24332150205575</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.00417397392624</v>
+        <v>24.00692035075266</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16544.9617319314</v>
+        <v>16547.1073831496</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06025503418402134</v>
+        <v>0.05478560416312184</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18926.90203180212</v>
+        <v>18927.19108084359</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2128975265017667</v>
+        <v>0.2065026362038664</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4301,6 +4301,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>15687.65</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.124913251323</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4341,7 +4374,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15687.65</v>
+        <v>15846.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.76</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.1268656716417911</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.2640597539543</v>
+        <v>689.2931709438888</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1249132513231015</v>
+        <v>0.1248979366797061</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04393673110720562</v>
+        <v>0.04349717268377556</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>87.31343283582089</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>69.96530052924059</v>
+        <v>69.95917467188242</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.24332150205575</v>
+        <v>82.10715538663935</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.00692035075266</v>
+        <v>24.00672974907657</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16547.1073831496</v>
+        <v>16547.67487273398</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05478560416312184</v>
+        <v>0.04422486946831561</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18927.19108084359</v>
+        <v>18927.99047411919</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2065026362038664</v>
+        <v>0.1944323618964769</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4334,6 +4334,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>15846.85</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.126865671642</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.12489793668</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4374,7 +4407,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15846.85</v>
+        <v>15734.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.99</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1268656716417911</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.2931709438888</v>
+        <v>689.2159439334209</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1248979366797061</v>
+        <v>0.1248369016961548</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04349717268377556</v>
+        <v>0.04380201489268506</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>87.31343283582089</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>69.95917467188242</v>
+        <v>69.93476067846191</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.10715538663935</v>
+        <v>85.23415954682216</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.00672974907657</v>
+        <v>24.00597012510986</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16547.67487273398</v>
+        <v>16545.29735981509</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04422486946831561</v>
+        <v>0.05150986093341481</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18927.99047411919</v>
+        <v>18925.86982041174</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1944323618964769</v>
+        <v>0.2028033289531319</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4367,6 +4367,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>15734.8</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.124836901696</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4407,7 +4440,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15734.8</v>
+        <v>15402.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.83</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.2159439334209</v>
+        <v>689.4427036705461</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1248369016961548</v>
+        <v>0.1252948948025503</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04380201489268506</v>
+        <v>0.04476275738585497</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>69.93476067846191</v>
+        <v>70.11795792102012</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.23415954682216</v>
+        <v>87.37867095839559</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.00597012510986</v>
+        <v>24.01167017645689</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16545.29735981509</v>
+        <v>16554.67080610185</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05150986093341481</v>
+        <v>0.0748285665379087</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18925.86982041174</v>
+        <v>18932.0966427932</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2028033289531319</v>
+        <v>0.2291853178155774</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4400,6 +4400,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>15402.15</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.125294894803</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4440,7 +4473,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15402.15</v>
+        <v>15600.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.34</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.4427036705461</v>
+        <v>689.3747238179408</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1252948948025503</v>
+        <v>0.1251001001050718</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04476275738585497</v>
+        <v>0.04418912947414936</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>70.11795792102012</v>
+        <v>70.04004004202871</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>87.37867095839559</v>
+        <v>86.31051947529517</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.01167017645689</v>
+        <v>24.00924581730769</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16554.67080610185</v>
+        <v>16551.36720438354</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0748285665379087</v>
+        <v>0.06094767199768847</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18932.0966427932</v>
+        <v>18930.22991604065</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2291853178155774</v>
+        <v>0.2134334953601416</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4433,6 +4433,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>15600.55</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.125100100105</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4473,7 +4506,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15600.55</v>
+        <v>15566.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.63</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.3747238179408</v>
+        <v>689.6876384581302</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1251001001050718</v>
+        <v>0.1253825669498161</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04418912947414936</v>
+        <v>0.04430660168365087</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>70.04004004202871</v>
+        <v>70.15302677992644</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>86.31051947529517</v>
+        <v>86.34441549666448</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.00924581730769</v>
+        <v>24.01276131895257</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16551.36720438354</v>
+        <v>16561.30464692714</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06094767199768847</v>
+        <v>0.06392385108341037</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18930.22991604065</v>
+        <v>18938.82255206026</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2134334953601416</v>
+        <v>0.2166592822330526</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4466,6 +4466,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>15566.25</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.12538256695</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4506,7 +4539,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15566.25</v>
+        <v>15755.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.57</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.6876384581302</v>
+        <v>689.8073555166375</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1253825669498161</v>
+        <v>0.1259001063503864</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04430660168365087</v>
+        <v>0.04378283712784588</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>70.15302677992644</v>
+        <v>70.36004254015455</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>86.34441549666448</v>
+        <v>85.36174410532993</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.01276131895257</v>
+        <v>24.01920246646367</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16561.30464692714</v>
+        <v>16568.62253501</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06392385108341037</v>
+        <v>0.05162882952993297</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18938.82255206026</v>
+        <v>18942.10998248687</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2166592822330526</v>
+        <v>0.202276707530648</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4499,6 +4499,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>15755.2</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.12590010635</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4539,7 +4572,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15755.2</v>
+        <v>15725.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.84</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.8073555166375</v>
+        <v>689.7105263157895</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1259001063503864</v>
+        <v>0.125778365699887</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04378283712784588</v>
+        <v>0.04385964912280702</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>70.36004254015455</v>
+        <v>70.31134627995479</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.36174410532993</v>
+        <v>85.34713522727002</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.01920246646367</v>
+        <v>24.01768731711059</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16568.62253501</v>
+        <v>16565.25176037241</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05162882952993297</v>
+        <v>0.05340733846976287</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18942.10998248687</v>
+        <v>18939.45105263158</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.202276707530648</v>
+        <v>0.2043859649122808</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4532,6 +4532,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>15725.4</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.1257783657</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4572,7 +4605,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15725.4</v>
+        <v>15801.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>689.7105263157895</v>
+        <v>690.6184440559441</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.125778365699887</v>
+        <v>0.1276157116796393</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04385964912280702</v>
+        <v>0.04370629370629371</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>88.80597014925374</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>70.31134627995479</v>
+        <v>71.0462846718557</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.34713522727002</v>
+        <v>83.47806450603431</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.01768731711059</v>
+        <v>24.05398727322408</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16565.25176037241</v>
+        <v>16612.1272639755</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05340733846976287</v>
+        <v>0.05131063257098267</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18939.45105263158</v>
+        <v>18964.38247377623</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2043859649122808</v>
+        <v>0.2001748251748252</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4565,6 +4565,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>15801.35</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.111940298507</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.12761571168</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4605,7 +4638,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15801.35</v>
+        <v>15843.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.88</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1119402985074627</v>
+        <v>0.1268656716417911</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>690.6184440559441</v>
+        <v>691.2369109947643</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1276157116796393</v>
+        <v>0.1302547091219106</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04370629370629371</v>
+        <v>0.04363001745200698</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.80597014925374</v>
+        <v>87.31343283582089</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.0462846718557</v>
+        <v>72.10188364876424</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.47806450603431</v>
+        <v>82.74996807970389</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.05398727322408</v>
+        <v>24.1286332008769</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16612.1272639755</v>
+        <v>16678.60188029986</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05131063257098267</v>
+        <v>0.05273268764733419</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>27.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18964.38247377623</v>
+        <v>18981.36557591623</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2001748251748252</v>
+        <v>0.1980802792321117</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4598,6 +4598,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>15843.15</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.126865671642</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.130254709122</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4638,7 +4671,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15843.15</v>
+        <v>15678.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.92</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1268656716417911</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>691.2369109947643</v>
+        <v>696.2144760213145</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1302547091219106</v>
+        <v>0.1371779272119906</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04363001745200698</v>
+        <v>0.04440497335701599</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>87.31343283582089</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.10188364876424</v>
+        <v>74.87117088479624</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.74996807970389</v>
+        <v>87.75985872812544</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.1286332008769</v>
+        <v>24.3102337314032</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16678.60188029986</v>
+        <v>16925.13663926457</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05273268764733419</v>
+        <v>0.07949528114579074</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.46</v>
+        <v>27.5434407576202</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>18981.36557591623</v>
+        <v>19176.14217489066</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1980802792321117</v>
+        <v>0.2230657530026732</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4631,6 +4631,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>15678.75</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.137177927212</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4671,7 +4704,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15678.75</v>
+        <v>15526.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.52</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>696.2144760213145</v>
+        <v>696.2757847533633</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1371779272119906</v>
+        <v>0.135513698534341</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04440497335701599</v>
+        <v>0.04484304932735426</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>74.87117088479624</v>
+        <v>74.20547941373641</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>87.75985872812544</v>
+        <v>88.60492740621048</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.3102337314032</v>
+        <v>24.2773874728285</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16925.13663926457</v>
+        <v>16903.75701440514</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07949528114579074</v>
+        <v>0.08867208398334081</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.5434407576202</v>
+        <v>27.5095475518651</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19176.14217489066</v>
+        <v>19154.23180988483</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2230657530026732</v>
+        <v>0.2336119978414841</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4664,6 +4664,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>15526.95</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.135513698534</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4704,7 +4737,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15526.95</v>
+        <v>15423.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>696.2757847533633</v>
+        <v>697.9072398190045</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.135513698534341</v>
+        <v>0.1381743390680845</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04484304932735426</v>
+        <v>0.04524886877828054</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>74.20547941373641</v>
+        <v>75.2697356272338</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>88.60492740621048</v>
+        <v>89.96898038966268</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.2773874728285</v>
+        <v>24.32939900173242</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16903.75701440514</v>
+        <v>16979.66370375432</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08867208398334081</v>
+        <v>0.1008777828838197</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.5095475518651</v>
+        <v>27.5637333967923</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19154.23180988483</v>
+        <v>19236.92909406223</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2336119978414841</v>
+        <v>0.2472277555109639</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4697,6 +4697,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>15423.75</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.138174339068</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4737,7 +4770,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15423.75</v>
+        <v>15209.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.1</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>697.9072398190045</v>
+        <v>698.3264462809917</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1381743390680845</v>
+        <v>0.1385392891276551</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04524886877828054</v>
+        <v>0.04591368227731864</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.2697356272338</v>
+        <v>75.41571565106204</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.96898038966268</v>
+        <v>91.05755051621414</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.32939900173242</v>
+        <v>24.33641855544964</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16979.66370375432</v>
+        <v>16994.76468503393</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1008777828838197</v>
+        <v>0.1173745893227567</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.5637333967923</v>
+        <v>27.57116586543407</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19236.92909406223</v>
+        <v>19253.67427863236</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2472277555109639</v>
+        <v>0.2658937495607931</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4730,6 +4730,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>15209.55</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.138539289128</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4770,7 +4803,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15209.55</v>
+        <v>15345.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.78</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>698.3264462809917</v>
+        <v>698.8023679417122</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1385392891276551</v>
+        <v>0.139535652488042</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04591368227731864</v>
+        <v>0.04553734061930783</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.41571565106204</v>
+        <v>75.8142609952168</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.05755051621414</v>
+        <v>91.17711411946055</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.33641855544964</v>
+        <v>24.35558289299857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16994.76468503393</v>
+        <v>17019.73899822806</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1173745893227567</v>
+        <v>0.1090884741802627</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.57116586543407</v>
+        <v>27.59145751695647</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19253.67427863236</v>
+        <v>19280.97584781233</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2658937495607931</v>
+        <v>0.256441599132808</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4763,6 +4763,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>15345.7</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.139535652488</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4803,7 +4836,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15345.7</v>
+        <v>15431.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.96</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>698.8023679417122</v>
+        <v>706.5911172161173</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.139535652488042</v>
+        <v>0.1522067681366572</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04553734061930783</v>
+        <v>0.04578754578754578</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>75.8142609952168</v>
+        <v>80.44135362733145</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.17711411946055</v>
+        <v>92.56524190909495</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.35558289299857</v>
+        <v>24.49520468727528</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17019.73899822806</v>
+        <v>17308.09404641932</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1090884741802627</v>
+        <v>0.1215753061939233</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.59145751695647</v>
+        <v>27.72430383143326</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19280.97584781233</v>
+        <v>19589.7468182915</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.256441599132808</v>
+        <v>0.2694278311095812</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4796,6 +4796,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>15431.95</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.152206768137</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4836,7 +4869,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7066,12 +7099,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>ICICI Life Insurance Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICILIFE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7086,12 +7119,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7106,12 +7139,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15431.95</v>
+        <v>15438.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>706.5911172161173</v>
+        <v>707.2308749427394</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1522067681366572</v>
+        <v>0.1505225672590236</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04578754578754578</v>
+        <v>0.04580852038479157</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.44135362733145</v>
+        <v>80.10451345180472</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.56524190909495</v>
+        <v>92.46418985643693</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.49520468727528</v>
+        <v>24.48948802829634</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17308.09404641932</v>
+        <v>17319.72204515176</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1215753061939233</v>
+        <v>0.1218272115573222</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.72430383143326</v>
+        <v>27.71550784725227</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19589.7468182915</v>
+        <v>19601.26286429458</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2694278311095812</v>
+        <v>0.2696064061957064</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4829,6 +4829,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>15438.85</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.150522567259</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4869,7 +4902,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15438.85</v>
+        <v>15588.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.83</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>707.2308749427394</v>
+        <v>706.9659863945578</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1505225672590236</v>
+        <v>0.1500234485237257</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04580852038479157</v>
+        <v>0.04535147392290249</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.10451345180472</v>
+        <v>80.00468970474515</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.46418985643693</v>
+        <v>91.38946661291608</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.48948802829634</v>
+        <v>24.48779387670339</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17319.72204515176</v>
+        <v>17312.03735267023</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1218272115573222</v>
+        <v>0.1105575454287253</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.71550784725227</v>
+        <v>27.71324897846166</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19601.26286429458</v>
+        <v>19592.32440025612</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2696064061957064</v>
+        <v>0.2568366883656081</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4862,6 +4862,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>15588.6</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.150023448524</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4902,7 +4935,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-largemidcap-250.xlsx
+++ b/docs/downloads/indices/nifty-largemidcap-250.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15588.6</v>
+        <v>15541.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.05</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>706.9659863945578</v>
+        <v>710.6332876085962</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1500234485237257</v>
+        <v>0.1561840298543917</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04535147392290249</v>
+        <v>0.04572473708276177</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.00468970474515</v>
+        <v>81.23680597087835</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.38946661291608</v>
+        <v>92.80387761215903</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.48779387670339</v>
+        <v>24.50870464990577</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>17312.03735267023</v>
+        <v>17416.70136039062</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1105575454287253</v>
+        <v>0.120654076356002</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>27.71324897846166</v>
+        <v>27.74905376292247</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19592.32440025612</v>
+        <v>19719.40130357328</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2568366883656081</v>
+        <v>0.2688181876050513</v>
       </c>
     </row>
     <row r="16">
@@ -3913,7 +3913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4895,6 +4895,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>15541.55</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.156184029854</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4935,7 +4968,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
